--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129930254</v>
+        <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373746</v>
+        <v>373532</v>
       </c>
       <c r="R3" t="n">
-        <v>6849900</v>
+        <v>6849866</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -896,43 +906,43 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129930254</t>
+          <t>https://artportalen.se/Sighting/136042732</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135791297</v>
+        <v>129930254</v>
       </c>
       <c r="B4" t="n">
-        <v>98144</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>373550</v>
+        <v>373746</v>
       </c>
       <c r="R4" t="n">
-        <v>6849899</v>
+        <v>6849900</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,22 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1017,43 +1017,43 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135791297</t>
+          <t>https://artportalen.se/Sighting/129930254</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129930256</v>
+        <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>79085</v>
+        <v>98144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>373741</v>
+        <v>373550</v>
       </c>
       <c r="R5" t="n">
-        <v>6849898</v>
+        <v>6849899</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,12 +1092,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1127,6 +1137,117 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135791297</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129930256</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Strömsillret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>373741</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6849898</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129930256</t>
         </is>
@@ -1138,6 +1259,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>135791297</v>
       </c>
       <c r="B5" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34304-2026 artfynd.xlsx
+++ b/artfynd/A 34304-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136042732</v>
       </c>
       <c r="B3" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
